--- a/DataAnalysis/TryingToPackStuffBetter/PreprocessingADV/LF/0.05/Results.xlsx
+++ b/DataAnalysis/TryingToPackStuffBetter/PreprocessingADV/LF/0.05/Results.xlsx
@@ -8,7 +8,7 @@
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\Utente\Desktop\CultureAwarenessTest\DataAnalysis\TryingToPackStuffBetter\PreprocessingADV\LF\0.05\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{80C62AB5-0AC0-4677-95C2-315F40365429}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EF418B16-D835-4283-9E31-33C65B4C5279}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-108" yWindow="-108" windowWidth="23256" windowHeight="12456" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -39,7 +39,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="82" uniqueCount="34">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="73" uniqueCount="30">
   <si>
     <t>Dati originali</t>
   </si>
@@ -47,9 +47,6 @@
     <t>ERR</t>
   </si>
   <si>
-    <t>STD</t>
-  </si>
-  <si>
     <t>NOAUG</t>
   </si>
   <si>
@@ -110,9 +107,6 @@
     <t>ERR_2_i</t>
   </si>
   <si>
-    <t>tau=10%</t>
-  </si>
-  <si>
     <t>ADV</t>
   </si>
   <si>
@@ -135,12 +129,6 @@
   </si>
   <si>
     <t>ep=0.0001</t>
-  </si>
-  <si>
-    <t>ep=0.01</t>
-  </si>
-  <si>
-    <t>ep=0.1</t>
   </si>
 </sst>
 </file>
@@ -459,202 +447,184 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:P7"/>
+  <dimension ref="A1:L7"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
-  <cols>
-    <col min="1" max="1" width="9.88671875" customWidth="1"/>
-  </cols>
   <sheetData>
-    <row r="1" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="A1" t="s">
+    <row r="1" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C1" t="s">
+        <v>3</v>
+      </c>
+      <c r="D1" t="s">
+        <v>4</v>
+      </c>
+      <c r="E1" t="s">
+        <v>5</v>
+      </c>
+      <c r="F1" t="s">
+        <v>6</v>
+      </c>
+      <c r="G1" t="s">
+        <v>7</v>
+      </c>
+      <c r="H1" t="s">
+        <v>8</v>
+      </c>
+      <c r="I1" t="s">
+        <v>1</v>
+      </c>
+      <c r="J1" t="s">
+        <v>12</v>
+      </c>
+      <c r="K1" t="s">
+        <v>14</v>
+      </c>
+      <c r="L1" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="2" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A2" t="s">
         <v>2</v>
       </c>
-      <c r="G1" t="s">
-        <v>4</v>
-      </c>
-      <c r="H1" t="s">
-        <v>5</v>
-      </c>
-      <c r="I1" t="s">
-        <v>6</v>
-      </c>
-      <c r="J1" t="s">
-        <v>7</v>
-      </c>
-      <c r="K1" t="s">
-        <v>8</v>
-      </c>
-      <c r="L1" t="s">
-        <v>9</v>
-      </c>
-      <c r="M1" t="s">
-        <v>1</v>
-      </c>
-      <c r="N1" t="s">
-        <v>13</v>
-      </c>
-      <c r="O1" t="s">
-        <v>15</v>
-      </c>
-      <c r="P1" t="s">
-        <v>16</v>
-      </c>
-    </row>
-    <row r="2" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C2" t="s">
-        <v>3</v>
+      <c r="C2" s="1">
+        <v>24.111111111111111</v>
+      </c>
+      <c r="D2" s="1">
+        <v>4.5878765361669318</v>
+      </c>
+      <c r="E2" s="1">
+        <v>13.555555555555555</v>
+      </c>
+      <c r="F2" s="1">
+        <v>3.1369217041197843</v>
       </c>
       <c r="G2" s="1">
-        <v>24.111111111111111</v>
+        <v>34.388888888888886</v>
       </c>
       <c r="H2" s="1">
-        <v>4.5878765361669318</v>
+        <v>4.1741599287893951</v>
       </c>
       <c r="I2" s="1">
-        <v>13.555555555555555</v>
+        <v>24.018518518518519</v>
       </c>
       <c r="J2" s="1">
-        <v>3.1369217041197843</v>
+        <v>3.0736835985829081</v>
       </c>
       <c r="K2" s="1">
-        <v>34.388888888888886</v>
+        <v>10.462962962962962</v>
       </c>
       <c r="L2" s="1">
-        <v>4.1741599287893951</v>
-      </c>
-      <c r="M2" s="1">
-        <v>24.018518518518519</v>
-      </c>
-      <c r="N2" s="1">
-        <v>3.0736835985829081</v>
-      </c>
-      <c r="O2" s="1">
-        <v>10.462962962962962</v>
-      </c>
-      <c r="P2" s="1">
         <v>3.259364476416144</v>
       </c>
     </row>
-    <row r="3" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="C3" t="s">
-        <v>24</v>
-      </c>
+    <row r="3" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="A3" t="s">
+        <v>22</v>
+      </c>
+      <c r="C3" s="1"/>
+      <c r="D3" s="1"/>
+      <c r="E3" s="1"/>
+      <c r="F3" s="1"/>
       <c r="G3" s="1"/>
       <c r="H3" s="1"/>
       <c r="I3" s="1"/>
       <c r="J3" s="1"/>
       <c r="K3" s="1"/>
       <c r="L3" s="1"/>
-      <c r="M3" s="1"/>
-      <c r="N3" s="1"/>
-      <c r="O3" s="1"/>
-      <c r="P3" s="1"/>
-    </row>
-    <row r="4" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D4" t="s">
-        <v>28</v>
-      </c>
-      <c r="G4" s="1"/>
-      <c r="H4" s="1"/>
-      <c r="I4" s="1"/>
-      <c r="J4" s="1"/>
-      <c r="K4" s="1"/>
-      <c r="L4" s="1"/>
-      <c r="M4" s="1"/>
-      <c r="N4" s="1"/>
-      <c r="O4" s="1"/>
-      <c r="P4" s="1"/>
-    </row>
-    <row r="5" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E5" t="s">
-        <v>23</v>
-      </c>
-      <c r="F5" t="s">
-        <v>33</v>
-      </c>
-      <c r="G5" s="1">
-        <v>22.375</v>
-      </c>
-      <c r="H5" s="1">
-        <v>3.5207716957129347</v>
-      </c>
-      <c r="I5" s="1">
-        <v>13.625</v>
-      </c>
-      <c r="J5" s="1">
-        <v>2.462214450449026</v>
-      </c>
-      <c r="K5" s="1">
-        <v>31.75</v>
-      </c>
-      <c r="L5" s="1">
-        <v>1.5</v>
-      </c>
-      <c r="M5" s="1">
-        <v>22.583333333333332</v>
-      </c>
-      <c r="N5" s="1">
-        <v>1.8383769008638104</v>
-      </c>
-      <c r="O5" s="1">
-        <v>8.9583333333333321</v>
-      </c>
-      <c r="P5" s="1">
-        <v>2.0744254001387374</v>
-      </c>
-    </row>
-    <row r="6" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="D6" t="s">
-        <v>29</v>
-      </c>
-      <c r="G6" s="1"/>
-      <c r="H6" s="1"/>
-      <c r="I6" s="1"/>
-      <c r="J6" s="1"/>
-      <c r="K6" s="1"/>
-      <c r="L6" s="1"/>
-      <c r="M6" s="1"/>
-      <c r="N6" s="1"/>
-      <c r="O6" s="1"/>
-      <c r="P6" s="1"/>
-    </row>
-    <row r="7" spans="1:16" x14ac:dyDescent="0.3">
-      <c r="E7" t="s">
-        <v>23</v>
-      </c>
-      <c r="F7" t="s">
-        <v>33</v>
-      </c>
-      <c r="G7" s="1">
-        <v>22.5</v>
-      </c>
-      <c r="H7" s="1">
-        <v>1.6832508230603465</v>
-      </c>
-      <c r="I7" s="1">
-        <v>13.25</v>
-      </c>
-      <c r="J7" s="1">
-        <v>2.1015867021530821</v>
-      </c>
-      <c r="K7" s="1">
-        <v>35.375</v>
-      </c>
-      <c r="L7" s="1">
-        <v>2.6575364531836625</v>
-      </c>
-      <c r="M7" s="1">
-        <v>23.708333333333332</v>
-      </c>
-      <c r="N7" s="1">
-        <v>0.43832593994609698</v>
-      </c>
-      <c r="O7" s="1">
-        <v>10.458333333333332</v>
-      </c>
-      <c r="P7" s="1">
-        <v>1.8627687476998984</v>
-      </c>
+    </row>
+    <row r="4" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B4" t="s">
+        <v>26</v>
+      </c>
+      <c r="C4" s="1">
+        <v>20.333333333333332</v>
+      </c>
+      <c r="D4" s="1">
+        <v>1.807392228230128</v>
+      </c>
+      <c r="E4" s="1">
+        <v>11.083333333333334</v>
+      </c>
+      <c r="F4" s="1">
+        <v>1.9853631070075506</v>
+      </c>
+      <c r="G4" s="1">
+        <v>27.583333333333332</v>
+      </c>
+      <c r="H4" s="1">
+        <v>2.615657979680575</v>
+      </c>
+      <c r="I4" s="1">
+        <v>19.666666666666668</v>
+      </c>
+      <c r="J4" s="1">
+        <v>1.3249737942901196</v>
+      </c>
+      <c r="K4" s="1">
+        <v>8.5833333333333339</v>
+      </c>
+      <c r="L4" s="1">
+        <v>1.0474837574980422</v>
+      </c>
+    </row>
+    <row r="5" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C5" s="1"/>
+      <c r="D5" s="1"/>
+      <c r="E5" s="1"/>
+      <c r="F5" s="1"/>
+      <c r="G5" s="1"/>
+      <c r="H5" s="1"/>
+      <c r="I5" s="1"/>
+      <c r="J5" s="1"/>
+      <c r="K5" s="1"/>
+      <c r="L5" s="1"/>
+    </row>
+    <row r="6" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="B6" t="s">
+        <v>27</v>
+      </c>
+      <c r="C6" s="1">
+        <v>20.416666666666668</v>
+      </c>
+      <c r="D6" s="1">
+        <v>3.8654452093732612</v>
+      </c>
+      <c r="E6" s="1">
+        <v>11.5</v>
+      </c>
+      <c r="F6" s="1">
+        <v>2.0248456731316584</v>
+      </c>
+      <c r="G6" s="1">
+        <v>33.5</v>
+      </c>
+      <c r="H6" s="1">
+        <v>3.5071355833500366</v>
+      </c>
+      <c r="I6" s="1">
+        <v>21.805555555555557</v>
+      </c>
+      <c r="J6" s="1">
+        <v>1.0822644299321198</v>
+      </c>
+      <c r="K6" s="1">
+        <v>10.305555555555555</v>
+      </c>
+      <c r="L6" s="1">
+        <v>2.9728711648779873</v>
+      </c>
+    </row>
+    <row r="7" spans="1:12" x14ac:dyDescent="0.3">
+      <c r="C7" s="1"/>
+      <c r="D7" s="1"/>
+      <c r="E7" s="1"/>
+      <c r="F7" s="1"/>
+      <c r="G7" s="1"/>
+      <c r="H7" s="1"/>
+      <c r="I7" s="1"/>
+      <c r="J7" s="1"/>
+      <c r="K7" s="1"/>
+      <c r="L7" s="1"/>
     </row>
   </sheetData>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
@@ -673,357 +643,374 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="K2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
+      <c r="Q2" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>20</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>21</v>
       </c>
-      <c r="S2" t="s">
-        <v>22</v>
-      </c>
       <c r="T2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W2" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="X2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB2" t="s">
         <v>25</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>27</v>
       </c>
       <c r="AC2" t="s">
         <v>1</v>
       </c>
       <c r="AD2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF2" t="s">
         <v>15</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B3">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="C3">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="D3">
-        <v>16</v>
+        <v>12</v>
       </c>
       <c r="E3">
-        <v>84</v>
+        <v>88</v>
       </c>
       <c r="G3">
-        <v>86</v>
+        <v>93</v>
       </c>
       <c r="H3">
-        <v>14</v>
+        <v>7</v>
       </c>
       <c r="I3">
-        <v>16</v>
+        <v>13</v>
       </c>
       <c r="J3">
-        <v>84</v>
+        <v>87</v>
       </c>
       <c r="L3">
-        <v>64</v>
+        <v>71</v>
       </c>
       <c r="M3">
-        <v>36</v>
+        <v>29</v>
       </c>
       <c r="N3">
-        <v>49</v>
+        <v>34</v>
       </c>
       <c r="O3">
-        <v>51</v>
+        <v>66</v>
       </c>
       <c r="Q3">
         <f>AVERAGE(C3:D3)</f>
-        <v>24</v>
+        <v>23</v>
       </c>
       <c r="R3">
         <f>AVERAGE(H3:I3)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="S3">
         <f>AVERAGE(M3:N3)</f>
-        <v>42.5</v>
+        <v>31.5</v>
       </c>
       <c r="T3">
         <f>AVERAGE(Q3:S3)</f>
-        <v>27.166666666666668</v>
+        <v>21.5</v>
       </c>
       <c r="U3">
         <f>MIN(Q3:S3)</f>
-        <v>15</v>
+        <v>10</v>
       </c>
       <c r="V3">
         <f>T3-U3</f>
-        <v>12.166666666666668</v>
+        <v>11.5</v>
       </c>
       <c r="W3">
-        <f>AVERAGE(Q3:Q4)</f>
-        <v>20.75</v>
+        <f>AVERAGE(Q3:Q11)</f>
+        <v>20.416666666666668</v>
       </c>
       <c r="X3">
-        <f>_xlfn.STDEV.S(Q3:Q4)</f>
-        <v>4.5961940777125587</v>
+        <f>_xlfn.STDEV.S(Q3:Q11)</f>
+        <v>3.8654452093732612</v>
       </c>
       <c r="Y3">
-        <f>AVERAGE(R3:R4)</f>
-        <v>13.5</v>
+        <f>AVERAGE(R3:R11)</f>
+        <v>11.5</v>
       </c>
       <c r="Z3">
-        <f>_xlfn.STDEV.S(R3:R4)</f>
-        <v>2.1213203435596424</v>
+        <f>_xlfn.STDEV.S(R3:R11)</f>
+        <v>2.0248456731316584</v>
       </c>
       <c r="AA3">
-        <f>AVERAGE(S3:S4)</f>
-        <v>37.5</v>
+        <f>AVERAGE(S3:S11)</f>
+        <v>33.5</v>
       </c>
       <c r="AB3">
-        <f>_xlfn.STDEV.S(S3:S4)</f>
-        <v>7.0710678118654755</v>
+        <f>_xlfn.STDEV.S(S3:S11)</f>
+        <v>3.5071355833500366</v>
       </c>
       <c r="AC3">
-        <f>AVERAGE(T3:T4)</f>
-        <v>23.916666666666668</v>
+        <f>AVERAGE(T3:T11)</f>
+        <v>21.805555555555557</v>
       </c>
       <c r="AD3">
-        <f>_xlfn.STDEV.S(T3:T4)</f>
-        <v>4.5961940777125587</v>
+        <f>_xlfn.STDEV.S(T3:T11)</f>
+        <v>1.0822644299321198</v>
       </c>
       <c r="AE3">
-        <f>AVERAGE(V3:V4)</f>
-        <v>10.416666666666668</v>
+        <f>AVERAGE(V3:V11)</f>
+        <v>10.305555555555555</v>
       </c>
       <c r="AF3">
-        <f>_xlfn.STDEV.S(V3:V4)</f>
-        <v>2.4748737341529106</v>
+        <f>_xlfn.STDEV.S(V3:V11)</f>
+        <v>2.9728711648779873</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>76</v>
+        <v>80</v>
       </c>
       <c r="C4">
-        <v>24</v>
+        <v>20</v>
       </c>
       <c r="D4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="E4">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="G4">
-        <v>89</v>
+        <v>87</v>
       </c>
       <c r="H4">
-        <v>11</v>
+        <v>13</v>
       </c>
       <c r="I4">
-        <v>13</v>
+        <v>17</v>
       </c>
       <c r="J4">
-        <v>87</v>
+        <v>83</v>
       </c>
       <c r="L4">
-        <v>73</v>
+        <v>82</v>
       </c>
       <c r="M4">
-        <v>27</v>
+        <v>18</v>
       </c>
       <c r="N4">
-        <v>38</v>
+        <v>41</v>
       </c>
       <c r="O4">
-        <v>62</v>
+        <v>59</v>
       </c>
       <c r="Q4">
-        <f t="shared" ref="Q4:Q14" si="0">AVERAGE(C4:D4)</f>
-        <v>17.5</v>
+        <f t="shared" ref="Q4:Q8" si="0">AVERAGE(C4:D4)</f>
+        <v>16.5</v>
       </c>
       <c r="R4">
-        <f t="shared" ref="R4:R14" si="1">AVERAGE(H4:I4)</f>
-        <v>12</v>
+        <f t="shared" ref="R4:R8" si="1">AVERAGE(H4:I4)</f>
+        <v>15</v>
       </c>
       <c r="S4">
-        <f t="shared" ref="S4:S14" si="2">AVERAGE(M4:N4)</f>
-        <v>32.5</v>
+        <f t="shared" ref="S4:S8" si="2">AVERAGE(M4:N4)</f>
+        <v>29.5</v>
       </c>
       <c r="T4">
-        <f t="shared" ref="T4:T14" si="3">AVERAGE(Q4:S4)</f>
-        <v>20.666666666666668</v>
+        <f t="shared" ref="T4:T8" si="3">AVERAGE(Q4:S4)</f>
+        <v>20.333333333333332</v>
       </c>
       <c r="U4">
-        <f t="shared" ref="U4:U14" si="4">MIN(Q4:S4)</f>
-        <v>12</v>
+        <f t="shared" ref="U4:U8" si="4">MIN(Q4:S4)</f>
+        <v>15</v>
       </c>
       <c r="V4">
-        <f t="shared" ref="V4:V14" si="5">T4-U4</f>
-        <v>8.6666666666666679</v>
+        <f t="shared" ref="V4:V8" si="5">T4-U4</f>
+        <v>5.3333333333333321</v>
       </c>
     </row>
     <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
+      <c r="B5">
+        <v>66</v>
+      </c>
+      <c r="C5">
+        <v>34</v>
+      </c>
+      <c r="D5">
+        <v>19</v>
+      </c>
+      <c r="E5">
+        <v>81</v>
+      </c>
+      <c r="G5">
+        <v>90</v>
+      </c>
+      <c r="H5">
+        <v>10</v>
+      </c>
+      <c r="I5">
+        <v>9</v>
+      </c>
+      <c r="J5">
+        <v>91</v>
+      </c>
+      <c r="L5">
+        <v>68</v>
+      </c>
+      <c r="M5">
         <v>32</v>
+      </c>
+      <c r="N5">
+        <v>37</v>
+      </c>
+      <c r="O5">
+        <v>63</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>26.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>34.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>23.5</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>14</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>71</v>
+        <v>78</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>22</v>
       </c>
       <c r="D6">
-        <v>15</v>
+        <v>18</v>
       </c>
       <c r="E6">
-        <v>85</v>
+        <v>82</v>
       </c>
       <c r="G6">
-        <v>90</v>
+        <v>89</v>
       </c>
       <c r="H6">
-        <v>10</v>
+        <v>11</v>
       </c>
       <c r="I6">
+        <v>14</v>
+      </c>
+      <c r="J6">
+        <v>86</v>
+      </c>
+      <c r="L6">
+        <v>73</v>
+      </c>
+      <c r="M6">
         <v>27</v>
       </c>
-      <c r="J6">
-        <v>73</v>
-      </c>
-      <c r="L6">
-        <v>83</v>
-      </c>
-      <c r="M6">
-        <v>17</v>
-      </c>
       <c r="N6">
-        <v>42</v>
+        <v>35</v>
       </c>
       <c r="O6">
-        <v>58</v>
+        <v>65</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R6">
         <f t="shared" si="1"/>
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="S6">
         <f t="shared" si="2"/>
-        <v>29.5</v>
+        <v>31</v>
       </c>
       <c r="T6">
         <f t="shared" si="3"/>
-        <v>23.333333333333332</v>
+        <v>21.166666666666668</v>
       </c>
       <c r="U6">
         <f t="shared" si="4"/>
-        <v>18.5</v>
+        <v>12.5</v>
       </c>
       <c r="V6">
         <f t="shared" si="5"/>
-        <v>4.8333333333333321</v>
-      </c>
-      <c r="W6">
-        <f>AVERAGE(Q6:Q9)</f>
-        <v>23.375</v>
-      </c>
-      <c r="X6">
-        <f>_xlfn.STDEV.S(Q6:Q9)</f>
-        <v>1.8874586088176875</v>
-      </c>
-      <c r="Y6">
-        <f>AVERAGE(R6:R9)</f>
-        <v>16.125</v>
-      </c>
-      <c r="Z6">
-        <f>_xlfn.STDEV.S(R6:R9)</f>
-        <v>3.1457643480294792</v>
-      </c>
-      <c r="AA6">
-        <f>AVERAGE(S6:S9)</f>
-        <v>33</v>
-      </c>
-      <c r="AB6">
-        <f>_xlfn.STDEV.S(S6:S9)</f>
-        <v>5.6124860801609122</v>
-      </c>
-      <c r="AC6">
-        <f>AVERAGE(T6:T9)</f>
-        <v>24.166666666666664</v>
-      </c>
-      <c r="AD6">
-        <f>_xlfn.STDEV.S(T6:T9)</f>
-        <v>2.1559564346591391</v>
-      </c>
-      <c r="AE6">
-        <f>AVERAGE(V6:V9)</f>
-        <v>8.0416666666666661</v>
-      </c>
-      <c r="AF6">
-        <f>_xlfn.STDEV.S(V6:V9)</f>
-        <v>3.4463480402905917</v>
+        <v>8.6666666666666679</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B7">
-        <v>71</v>
+        <v>79</v>
       </c>
       <c r="C7">
-        <v>29</v>
+        <v>21</v>
       </c>
       <c r="D7">
-        <v>15</v>
+        <v>19</v>
       </c>
       <c r="E7">
-        <v>85</v>
+        <v>81</v>
       </c>
       <c r="G7">
-        <v>90</v>
+        <v>92</v>
       </c>
       <c r="H7">
-        <v>10</v>
+        <v>8</v>
       </c>
       <c r="I7">
         <v>13</v>
@@ -1032,457 +1019,102 @@
         <v>87</v>
       </c>
       <c r="L7">
-        <v>63</v>
+        <v>65</v>
       </c>
       <c r="M7">
-        <v>37</v>
+        <v>35</v>
       </c>
       <c r="N7">
-        <v>37</v>
+        <v>36</v>
       </c>
       <c r="O7">
-        <v>63</v>
+        <v>64</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>22</v>
+        <v>20</v>
       </c>
       <c r="R7">
         <f t="shared" si="1"/>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="S7">
         <f t="shared" si="2"/>
-        <v>37</v>
+        <v>35.5</v>
       </c>
       <c r="T7">
         <f t="shared" si="3"/>
-        <v>23.5</v>
+        <v>22</v>
       </c>
       <c r="U7">
         <f t="shared" si="4"/>
-        <v>11.5</v>
+        <v>10.5</v>
       </c>
       <c r="V7">
         <f t="shared" si="5"/>
-        <v>12</v>
+        <v>11.5</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>64</v>
+        <v>84</v>
       </c>
       <c r="C8">
-        <v>36</v>
+        <v>16</v>
       </c>
       <c r="D8">
-        <v>16</v>
+        <v>17</v>
       </c>
       <c r="E8">
-        <v>84</v>
+        <v>83</v>
       </c>
       <c r="G8">
-        <v>87</v>
+        <v>89</v>
       </c>
       <c r="H8">
-        <v>13</v>
+        <v>11</v>
       </c>
       <c r="I8">
-        <v>22</v>
+        <v>12</v>
       </c>
       <c r="J8">
-        <v>78</v>
+        <v>88</v>
       </c>
       <c r="L8">
-        <v>80</v>
+        <v>66</v>
       </c>
       <c r="M8">
-        <v>20</v>
+        <v>34</v>
       </c>
       <c r="N8">
-        <v>57</v>
+        <v>44</v>
       </c>
       <c r="O8">
-        <v>43</v>
+        <v>56</v>
       </c>
       <c r="Q8">
         <f t="shared" si="0"/>
-        <v>26</v>
+        <v>16.5</v>
       </c>
       <c r="R8">
         <f t="shared" si="1"/>
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="S8">
         <f t="shared" si="2"/>
-        <v>38.5</v>
+        <v>39</v>
       </c>
       <c r="T8">
         <f t="shared" si="3"/>
-        <v>27.333333333333332</v>
+        <v>22.333333333333332</v>
       </c>
       <c r="U8">
         <f t="shared" si="4"/>
-        <v>17.5</v>
+        <v>11.5</v>
       </c>
       <c r="V8">
         <f t="shared" si="5"/>
-        <v>9.8333333333333321</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>67</v>
-      </c>
-      <c r="C9">
-        <v>33</v>
-      </c>
-      <c r="D9">
-        <v>14</v>
-      </c>
-      <c r="E9">
-        <v>86</v>
-      </c>
-      <c r="G9">
-        <v>80</v>
-      </c>
-      <c r="H9">
-        <v>20</v>
-      </c>
-      <c r="I9">
-        <v>14</v>
-      </c>
-      <c r="J9">
-        <v>86</v>
-      </c>
-      <c r="L9">
-        <v>87</v>
-      </c>
-      <c r="M9">
-        <v>13</v>
-      </c>
-      <c r="N9">
-        <v>41</v>
-      </c>
-      <c r="O9">
-        <v>59</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>23.5</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>17</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>27</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="3"/>
-        <v>22.5</v>
-      </c>
-      <c r="U9">
-        <f t="shared" si="4"/>
-        <v>17</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="5"/>
-        <v>5.5</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <v>72</v>
-      </c>
-      <c r="C11">
-        <v>28</v>
-      </c>
-      <c r="D11">
-        <v>15</v>
-      </c>
-      <c r="E11">
-        <v>85</v>
-      </c>
-      <c r="G11">
-        <v>90</v>
-      </c>
-      <c r="H11">
-        <v>10</v>
-      </c>
-      <c r="I11">
-        <v>12</v>
-      </c>
-      <c r="J11">
-        <v>88</v>
-      </c>
-      <c r="L11">
-        <v>73</v>
-      </c>
-      <c r="M11">
-        <v>27</v>
-      </c>
-      <c r="N11">
-        <v>50</v>
-      </c>
-      <c r="O11">
-        <v>50</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="0"/>
-        <v>21.5</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="1"/>
-        <v>11</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="2"/>
-        <v>38.5</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="3"/>
-        <v>23.666666666666668</v>
-      </c>
-      <c r="U11">
-        <f t="shared" si="4"/>
-        <v>11</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="5"/>
-        <v>12.666666666666668</v>
-      </c>
-      <c r="W11">
-        <f>AVERAGE(Q11:Q14)</f>
-        <v>22.5</v>
-      </c>
-      <c r="X11">
-        <f>_xlfn.STDEV.S(Q11:Q14)</f>
-        <v>1.6832508230603465</v>
-      </c>
-      <c r="Y11">
-        <f>AVERAGE(R11:R14)</f>
-        <v>13.25</v>
-      </c>
-      <c r="Z11">
-        <f>_xlfn.STDEV.S(R11:R14)</f>
-        <v>2.1015867021530821</v>
-      </c>
-      <c r="AA11">
-        <f>AVERAGE(S11:S14)</f>
-        <v>35.375</v>
-      </c>
-      <c r="AB11">
-        <f>_xlfn.STDEV.S(S11:S14)</f>
-        <v>2.6575364531836625</v>
-      </c>
-      <c r="AC11">
-        <f>AVERAGE(T11:T14)</f>
-        <v>23.708333333333332</v>
-      </c>
-      <c r="AD11">
-        <f>_xlfn.STDEV.S(T11:T14)</f>
-        <v>0.43832593994609698</v>
-      </c>
-      <c r="AE11">
-        <f>AVERAGE(V11:V14)</f>
-        <v>10.458333333333332</v>
-      </c>
-      <c r="AF11">
-        <f>_xlfn.STDEV.S(V11:V14)</f>
-        <v>1.8627687476998984</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B12">
-        <v>71</v>
-      </c>
-      <c r="C12">
-        <v>29</v>
-      </c>
-      <c r="D12">
-        <v>14</v>
-      </c>
-      <c r="E12">
-        <v>86</v>
-      </c>
-      <c r="G12">
-        <v>87</v>
-      </c>
-      <c r="H12">
-        <v>13</v>
-      </c>
-      <c r="I12">
-        <v>11</v>
-      </c>
-      <c r="J12">
-        <v>89</v>
-      </c>
-      <c r="L12">
-        <v>68</v>
-      </c>
-      <c r="M12">
-        <v>32</v>
-      </c>
-      <c r="N12">
-        <v>41</v>
-      </c>
-      <c r="O12">
-        <v>59</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="0"/>
-        <v>21.5</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="1"/>
-        <v>12</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="2"/>
-        <v>36.5</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="3"/>
-        <v>23.333333333333332</v>
-      </c>
-      <c r="U12">
-        <f t="shared" si="4"/>
-        <v>12</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="5"/>
-        <v>11.333333333333332</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B13">
-        <v>73</v>
-      </c>
-      <c r="C13">
-        <v>27</v>
-      </c>
-      <c r="D13">
-        <v>23</v>
-      </c>
-      <c r="E13">
-        <v>77</v>
-      </c>
-      <c r="G13">
-        <v>84</v>
-      </c>
-      <c r="H13">
-        <v>16</v>
-      </c>
-      <c r="I13">
-        <v>15</v>
-      </c>
-      <c r="J13">
-        <v>85</v>
-      </c>
-      <c r="L13">
-        <v>72</v>
-      </c>
-      <c r="M13">
-        <v>28</v>
-      </c>
-      <c r="N13">
-        <v>37</v>
-      </c>
-      <c r="O13">
-        <v>63</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="1"/>
-        <v>15.5</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="2"/>
-        <v>32.5</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="3"/>
-        <v>24.333333333333332</v>
-      </c>
-      <c r="U13">
-        <f t="shared" si="4"/>
-        <v>15.5</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="5"/>
-        <v>8.8333333333333321</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B14">
-        <v>68</v>
-      </c>
-      <c r="C14">
-        <v>32</v>
-      </c>
-      <c r="D14">
-        <v>12</v>
-      </c>
-      <c r="E14">
-        <v>88</v>
-      </c>
-      <c r="G14">
-        <v>86</v>
-      </c>
-      <c r="H14">
-        <v>14</v>
-      </c>
-      <c r="I14">
-        <v>15</v>
-      </c>
-      <c r="J14">
-        <v>85</v>
-      </c>
-      <c r="L14">
-        <v>79</v>
-      </c>
-      <c r="M14">
-        <v>21</v>
-      </c>
-      <c r="N14">
-        <v>47</v>
-      </c>
-      <c r="O14">
-        <v>53</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="0"/>
-        <v>22</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="1"/>
-        <v>14.5</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="2"/>
-        <v>34</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="3"/>
-        <v>23.5</v>
-      </c>
-      <c r="U14">
-        <f t="shared" si="4"/>
-        <v>14.5</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="5"/>
-        <v>9</v>
+        <v>10.833333333333332</v>
       </c>
     </row>
     <row r="31" spans="17:26" x14ac:dyDescent="0.3">
@@ -1673,86 +1305,86 @@
   <sheetData>
     <row r="1" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A1" t="s">
-        <v>31</v>
+        <v>29</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
+        <v>16</v>
+      </c>
+      <c r="F2" t="s">
         <v>17</v>
       </c>
-      <c r="F2" t="s">
+      <c r="K2" t="s">
         <v>18</v>
       </c>
-      <c r="K2" t="s">
+      <c r="Q2" t="s">
         <v>19</v>
       </c>
-      <c r="Q2" t="s">
+      <c r="R2" t="s">
         <v>20</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>21</v>
       </c>
-      <c r="S2" t="s">
-        <v>22</v>
-      </c>
       <c r="T2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W2" t="s">
-        <v>4</v>
+        <v>28</v>
       </c>
       <c r="X2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB2" t="s">
         <v>25</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>27</v>
       </c>
       <c r="AC2" t="s">
         <v>1</v>
       </c>
       <c r="AD2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF2" t="s">
         <v>15</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B3">
-        <v>64</v>
+        <v>68</v>
       </c>
       <c r="C3">
-        <v>36</v>
+        <v>32</v>
       </c>
       <c r="D3">
-        <v>10</v>
+        <v>15</v>
       </c>
       <c r="E3">
-        <v>90</v>
+        <v>85</v>
       </c>
       <c r="G3">
-        <v>86</v>
+        <v>87</v>
       </c>
       <c r="H3">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="I3">
         <v>6</v>
@@ -1767,319 +1399,336 @@
         <v>28</v>
       </c>
       <c r="N3">
-        <v>35</v>
+        <v>23</v>
       </c>
       <c r="O3">
-        <v>65</v>
+        <v>77</v>
       </c>
       <c r="Q3">
         <f>AVERAGE(C3:D3)</f>
-        <v>23</v>
+        <v>23.5</v>
       </c>
       <c r="R3">
         <f>AVERAGE(H3:I3)</f>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="S3">
         <f>AVERAGE(M3:N3)</f>
-        <v>31.5</v>
+        <v>25.5</v>
       </c>
       <c r="T3">
         <f>AVERAGE(Q3:S3)</f>
-        <v>21.5</v>
+        <v>19.5</v>
       </c>
       <c r="U3">
         <f>MIN(Q3:S3)</f>
-        <v>10</v>
+        <v>9.5</v>
       </c>
       <c r="V3">
         <f>T3-U3</f>
-        <v>11.5</v>
+        <v>10</v>
       </c>
       <c r="W3">
-        <f>AVERAGE(Q3:Q4)</f>
-        <v>24</v>
+        <f>AVERAGE(Q3:Q11)</f>
+        <v>20.333333333333332</v>
       </c>
       <c r="X3">
-        <f>_xlfn.STDEV.S(Q3:Q4)</f>
-        <v>1.4142135623730951</v>
+        <f>_xlfn.STDEV.S(Q3:Q11)</f>
+        <v>1.807392228230128</v>
       </c>
       <c r="Y3">
-        <f>AVERAGE(R3:R4)</f>
-        <v>13</v>
+        <f>AVERAGE(R3:R11)</f>
+        <v>11.083333333333334</v>
       </c>
       <c r="Z3">
-        <f>_xlfn.STDEV.S(R3:R4)</f>
-        <v>4.2426406871192848</v>
+        <f>_xlfn.STDEV.S(R3:R11)</f>
+        <v>1.9853631070075506</v>
       </c>
       <c r="AA3">
-        <f>AVERAGE(S3:S4)</f>
-        <v>32.5</v>
+        <f>AVERAGE(S3:S11)</f>
+        <v>27.583333333333332</v>
       </c>
       <c r="AB3">
-        <f>_xlfn.STDEV.S(S3:S4)</f>
-        <v>1.4142135623730951</v>
+        <f>_xlfn.STDEV.S(S3:S11)</f>
+        <v>2.615657979680575</v>
       </c>
       <c r="AC3">
-        <f>AVERAGE(T3:T4)</f>
-        <v>23.166666666666664</v>
+        <f>AVERAGE(T3:T11)</f>
+        <v>19.666666666666668</v>
       </c>
       <c r="AD3">
-        <f>_xlfn.STDEV.S(T3:T4)</f>
-        <v>2.3570226039551576</v>
+        <f>_xlfn.STDEV.S(T3:T11)</f>
+        <v>1.3249737942901196</v>
       </c>
       <c r="AE3">
-        <f>AVERAGE(V3:V4)</f>
-        <v>10.166666666666666</v>
+        <f>AVERAGE(V3:V11)</f>
+        <v>8.5833333333333339</v>
       </c>
       <c r="AF3">
-        <f>_xlfn.STDEV.S(V3:V4)</f>
-        <v>1.8856180831641309</v>
+        <f>_xlfn.STDEV.S(V3:V11)</f>
+        <v>1.0474837574980422</v>
       </c>
     </row>
     <row r="4" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B4">
-        <v>68</v>
+        <v>76</v>
       </c>
       <c r="C4">
-        <v>32</v>
+        <v>24</v>
       </c>
       <c r="D4">
+        <v>14</v>
+      </c>
+      <c r="E4">
+        <v>86</v>
+      </c>
+      <c r="G4">
+        <v>98</v>
+      </c>
+      <c r="H4">
+        <v>2</v>
+      </c>
+      <c r="I4">
+        <v>16</v>
+      </c>
+      <c r="J4">
+        <v>84</v>
+      </c>
+      <c r="L4">
+        <v>76</v>
+      </c>
+      <c r="M4">
+        <v>24</v>
+      </c>
+      <c r="N4">
+        <v>25</v>
+      </c>
+      <c r="O4">
+        <v>75</v>
+      </c>
+      <c r="Q4">
+        <f t="shared" ref="Q4:Q8" si="0">AVERAGE(C4:D4)</f>
+        <v>19</v>
+      </c>
+      <c r="R4">
+        <f t="shared" ref="R4:R8" si="1">AVERAGE(H4:I4)</f>
+        <v>9</v>
+      </c>
+      <c r="S4">
+        <f t="shared" ref="S4:S8" si="2">AVERAGE(M4:N4)</f>
+        <v>24.5</v>
+      </c>
+      <c r="T4">
+        <f t="shared" ref="T4:T8" si="3">AVERAGE(Q4:S4)</f>
+        <v>17.5</v>
+      </c>
+      <c r="U4">
+        <f t="shared" ref="U4:U8" si="4">MIN(Q4:S4)</f>
+        <v>9</v>
+      </c>
+      <c r="V4">
+        <f t="shared" ref="V4:V8" si="5">T4-U4</f>
+        <v>8.5</v>
+      </c>
+    </row>
+    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
+      <c r="B5">
+        <v>81</v>
+      </c>
+      <c r="C5">
+        <v>19</v>
+      </c>
+      <c r="D5">
+        <v>20</v>
+      </c>
+      <c r="E5">
+        <v>80</v>
+      </c>
+      <c r="G5">
+        <v>96</v>
+      </c>
+      <c r="H5">
+        <v>4</v>
+      </c>
+      <c r="I5">
+        <v>15</v>
+      </c>
+      <c r="J5">
+        <v>85</v>
+      </c>
+      <c r="L5">
+        <v>82</v>
+      </c>
+      <c r="M5">
         <v>18</v>
       </c>
-      <c r="E4">
-        <v>82</v>
-      </c>
-      <c r="G4">
-        <v>83</v>
-      </c>
-      <c r="H4">
-        <v>17</v>
-      </c>
-      <c r="I4">
-        <v>15</v>
-      </c>
-      <c r="J4">
-        <v>85</v>
-      </c>
-      <c r="L4">
-        <v>79</v>
-      </c>
-      <c r="M4">
-        <v>21</v>
-      </c>
-      <c r="N4">
-        <v>46</v>
-      </c>
-      <c r="O4">
-        <v>54</v>
-      </c>
-      <c r="Q4">
-        <f t="shared" ref="Q4:Q14" si="0">AVERAGE(C4:D4)</f>
-        <v>25</v>
-      </c>
-      <c r="R4">
-        <f t="shared" ref="R4:R14" si="1">AVERAGE(H4:I4)</f>
-        <v>16</v>
-      </c>
-      <c r="S4">
-        <f t="shared" ref="S4:S14" si="2">AVERAGE(M4:N4)</f>
-        <v>33.5</v>
-      </c>
-      <c r="T4">
-        <f t="shared" ref="T4:T14" si="3">AVERAGE(Q4:S4)</f>
-        <v>24.833333333333332</v>
-      </c>
-      <c r="U4">
-        <f t="shared" ref="U4:U14" si="4">MIN(Q4:S4)</f>
-        <v>16</v>
-      </c>
-      <c r="V4">
-        <f t="shared" ref="V4:V14" si="5">T4-U4</f>
-        <v>8.8333333333333321</v>
-      </c>
-    </row>
-    <row r="5" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A5" t="s">
-        <v>32</v>
+      <c r="N5">
+        <v>37</v>
+      </c>
+      <c r="O5">
+        <v>63</v>
+      </c>
+      <c r="Q5">
+        <f t="shared" si="0"/>
+        <v>19.5</v>
+      </c>
+      <c r="R5">
+        <f t="shared" si="1"/>
+        <v>9.5</v>
+      </c>
+      <c r="S5">
+        <f t="shared" si="2"/>
+        <v>27.5</v>
+      </c>
+      <c r="T5">
+        <f t="shared" si="3"/>
+        <v>18.833333333333332</v>
+      </c>
+      <c r="U5">
+        <f t="shared" si="4"/>
+        <v>9.5</v>
+      </c>
+      <c r="V5">
+        <f t="shared" si="5"/>
+        <v>9.3333333333333321</v>
       </c>
     </row>
     <row r="6" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B6">
-        <v>71</v>
+        <v>69</v>
       </c>
       <c r="C6">
-        <v>29</v>
+        <v>31</v>
       </c>
       <c r="D6">
+        <v>11</v>
+      </c>
+      <c r="E6">
+        <v>89</v>
+      </c>
+      <c r="G6">
+        <v>89</v>
+      </c>
+      <c r="H6">
+        <v>11</v>
+      </c>
+      <c r="I6">
         <v>16</v>
       </c>
-      <c r="E6">
+      <c r="J6">
         <v>84</v>
       </c>
-      <c r="G6">
-        <v>91</v>
-      </c>
-      <c r="H6">
-        <v>9</v>
-      </c>
-      <c r="I6">
-        <v>14</v>
-      </c>
-      <c r="J6">
-        <v>86</v>
-      </c>
       <c r="L6">
-        <v>68</v>
+        <v>66</v>
       </c>
       <c r="M6">
-        <v>32</v>
+        <v>34</v>
       </c>
       <c r="N6">
-        <v>37</v>
+        <v>21</v>
       </c>
       <c r="O6">
-        <v>63</v>
+        <v>79</v>
       </c>
       <c r="Q6">
         <f t="shared" si="0"/>
-        <v>22.5</v>
+        <v>21</v>
       </c>
       <c r="R6">
         <f t="shared" si="1"/>
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="S6">
         <f t="shared" si="2"/>
-        <v>34.5</v>
+        <v>27.5</v>
       </c>
       <c r="T6">
         <f t="shared" si="3"/>
-        <v>22.833333333333332</v>
+        <v>20.666666666666668</v>
       </c>
       <c r="U6">
         <f t="shared" si="4"/>
-        <v>11.5</v>
+        <v>13.5</v>
       </c>
       <c r="V6">
         <f t="shared" si="5"/>
-        <v>11.333333333333332</v>
-      </c>
-      <c r="W6">
-        <f>AVERAGE(Q6:Q9)</f>
-        <v>24.375</v>
-      </c>
-      <c r="X6">
-        <f>_xlfn.STDEV.S(Q6:Q9)</f>
-        <v>1.25</v>
-      </c>
-      <c r="Y6">
-        <f>AVERAGE(R6:R9)</f>
-        <v>13.625</v>
-      </c>
-      <c r="Z6">
-        <f>_xlfn.STDEV.S(R6:R9)</f>
-        <v>1.9311050377094112</v>
-      </c>
-      <c r="AA6">
-        <f>AVERAGE(S6:S9)</f>
-        <v>34.5</v>
-      </c>
-      <c r="AB6">
-        <f>_xlfn.STDEV.S(S6:S9)</f>
-        <v>2.2730302828309759</v>
-      </c>
-      <c r="AC6">
-        <f>AVERAGE(T6:T9)</f>
-        <v>24.166666666666668</v>
-      </c>
-      <c r="AD6">
-        <f>_xlfn.STDEV.S(T6:T9)</f>
-        <v>1.4593250596181897</v>
-      </c>
-      <c r="AE6">
-        <f>AVERAGE(V6:V9)</f>
-        <v>10.541666666666668</v>
-      </c>
-      <c r="AF6">
-        <f>_xlfn.STDEV.S(V6:V9)</f>
-        <v>0.6854979266251694</v>
+        <v>7.1666666666666679</v>
       </c>
     </row>
     <row r="7" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B7">
-        <v>63</v>
+        <v>75</v>
       </c>
       <c r="C7">
-        <v>37</v>
+        <v>25</v>
       </c>
       <c r="D7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="E7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="G7">
-        <v>87</v>
+        <v>88</v>
       </c>
       <c r="H7">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="I7">
-        <v>18</v>
+        <v>12</v>
       </c>
       <c r="J7">
-        <v>82</v>
+        <v>88</v>
       </c>
       <c r="L7">
-        <v>69</v>
+        <v>53</v>
       </c>
       <c r="M7">
-        <v>31</v>
+        <v>47</v>
       </c>
       <c r="N7">
-        <v>39</v>
+        <v>17</v>
       </c>
       <c r="O7">
-        <v>61</v>
+        <v>83</v>
       </c>
       <c r="Q7">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>18.5</v>
       </c>
       <c r="R7">
         <f t="shared" si="1"/>
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="S7">
         <f t="shared" si="2"/>
-        <v>35</v>
+        <v>32</v>
       </c>
       <c r="T7">
         <f t="shared" si="3"/>
-        <v>25.166666666666668</v>
+        <v>20.833333333333332</v>
       </c>
       <c r="U7">
         <f t="shared" si="4"/>
-        <v>15.5</v>
+        <v>12</v>
       </c>
       <c r="V7">
         <f t="shared" si="5"/>
-        <v>9.6666666666666679</v>
+        <v>8.8333333333333321</v>
       </c>
     </row>
     <row r="8" spans="1:32" x14ac:dyDescent="0.3">
       <c r="B8">
-        <v>63</v>
+        <v>74</v>
       </c>
       <c r="C8">
-        <v>37</v>
+        <v>26</v>
       </c>
       <c r="D8">
-        <v>13</v>
+        <v>15</v>
       </c>
       <c r="E8">
-        <v>87</v>
+        <v>85</v>
       </c>
       <c r="G8">
         <v>89</v>
@@ -2088,401 +1737,46 @@
         <v>11</v>
       </c>
       <c r="I8">
-        <v>14</v>
+        <v>15</v>
       </c>
       <c r="J8">
-        <v>86</v>
+        <v>85</v>
       </c>
       <c r="L8">
-        <v>74</v>
+        <v>85</v>
       </c>
       <c r="M8">
-        <v>26</v>
+        <v>15</v>
       </c>
       <c r="N8">
-        <v>37</v>
+        <v>42</v>
       </c>
       <c r="O8">
-        <v>63</v>
+        <v>58</v>
       </c>
       <c r="Q8">
         <f t="shared" si="0"/>
-        <v>25</v>
+        <v>20.5</v>
       </c>
       <c r="R8">
         <f t="shared" si="1"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="S8">
         <f t="shared" si="2"/>
-        <v>31.5</v>
+        <v>28.5</v>
       </c>
       <c r="T8">
         <f t="shared" si="3"/>
-        <v>23</v>
+        <v>20.666666666666668</v>
       </c>
       <c r="U8">
         <f t="shared" si="4"/>
-        <v>12.5</v>
+        <v>13</v>
       </c>
       <c r="V8">
         <f t="shared" si="5"/>
-        <v>10.5</v>
-      </c>
-    </row>
-    <row r="9" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B9">
-        <v>60</v>
-      </c>
-      <c r="C9">
-        <v>40</v>
-      </c>
-      <c r="D9">
-        <v>10</v>
-      </c>
-      <c r="E9">
-        <v>90</v>
-      </c>
-      <c r="G9">
-        <v>87</v>
-      </c>
-      <c r="H9">
-        <v>13</v>
-      </c>
-      <c r="I9">
-        <v>17</v>
-      </c>
-      <c r="J9">
-        <v>83</v>
-      </c>
-      <c r="L9">
-        <v>65</v>
-      </c>
-      <c r="M9">
-        <v>35</v>
-      </c>
-      <c r="N9">
-        <v>39</v>
-      </c>
-      <c r="O9">
-        <v>61</v>
-      </c>
-      <c r="Q9">
-        <f t="shared" si="0"/>
-        <v>25</v>
-      </c>
-      <c r="R9">
-        <f t="shared" si="1"/>
-        <v>15</v>
-      </c>
-      <c r="S9">
-        <f t="shared" si="2"/>
-        <v>37</v>
-      </c>
-      <c r="T9">
-        <f t="shared" si="3"/>
-        <v>25.666666666666668</v>
-      </c>
-      <c r="U9">
-        <f t="shared" si="4"/>
-        <v>15</v>
-      </c>
-      <c r="V9">
-        <f t="shared" si="5"/>
-        <v>10.666666666666668</v>
-      </c>
-    </row>
-    <row r="10" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="A10" t="s">
-        <v>33</v>
-      </c>
-    </row>
-    <row r="11" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B11">
-        <v>74</v>
-      </c>
-      <c r="C11">
-        <v>26</v>
-      </c>
-      <c r="D11">
-        <v>13</v>
-      </c>
-      <c r="E11">
-        <v>87</v>
-      </c>
-      <c r="G11">
-        <v>89</v>
-      </c>
-      <c r="H11">
-        <v>11</v>
-      </c>
-      <c r="I11">
-        <v>16</v>
-      </c>
-      <c r="J11">
-        <v>84</v>
-      </c>
-      <c r="L11">
-        <v>69</v>
-      </c>
-      <c r="M11">
-        <v>31</v>
-      </c>
-      <c r="N11">
-        <v>34</v>
-      </c>
-      <c r="O11">
-        <v>66</v>
-      </c>
-      <c r="Q11">
-        <f t="shared" si="0"/>
-        <v>19.5</v>
-      </c>
-      <c r="R11">
-        <f t="shared" si="1"/>
-        <v>13.5</v>
-      </c>
-      <c r="S11">
-        <f t="shared" si="2"/>
-        <v>32.5</v>
-      </c>
-      <c r="T11">
-        <f t="shared" si="3"/>
-        <v>21.833333333333332</v>
-      </c>
-      <c r="U11">
-        <f t="shared" si="4"/>
-        <v>13.5</v>
-      </c>
-      <c r="V11">
-        <f t="shared" si="5"/>
-        <v>8.3333333333333321</v>
-      </c>
-      <c r="W11">
-        <f>AVERAGE(Q11:Q14)</f>
-        <v>22.375</v>
-      </c>
-      <c r="X11">
-        <f>_xlfn.STDEV.S(Q11:Q14)</f>
-        <v>3.5207716957129347</v>
-      </c>
-      <c r="Y11">
-        <f>AVERAGE(R11:R14)</f>
-        <v>13.625</v>
-      </c>
-      <c r="Z11">
-        <f>_xlfn.STDEV.S(R11:R14)</f>
-        <v>2.462214450449026</v>
-      </c>
-      <c r="AA11">
-        <f>AVERAGE(S11:S14)</f>
-        <v>31.75</v>
-      </c>
-      <c r="AB11">
-        <f>_xlfn.STDEV.S(S11:S14)</f>
-        <v>1.5</v>
-      </c>
-      <c r="AC11">
-        <f>AVERAGE(T11:T14)</f>
-        <v>22.583333333333332</v>
-      </c>
-      <c r="AD11">
-        <f>_xlfn.STDEV.S(T11:T14)</f>
-        <v>1.8383769008638104</v>
-      </c>
-      <c r="AE11">
-        <f>AVERAGE(V11:V14)</f>
-        <v>8.9583333333333321</v>
-      </c>
-      <c r="AF11">
-        <f>_xlfn.STDEV.S(V11:V14)</f>
-        <v>2.0744254001387374</v>
-      </c>
-    </row>
-    <row r="12" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B12">
-        <v>67</v>
-      </c>
-      <c r="C12">
-        <v>33</v>
-      </c>
-      <c r="D12">
-        <v>10</v>
-      </c>
-      <c r="E12">
-        <v>90</v>
-      </c>
-      <c r="G12">
-        <v>82</v>
-      </c>
-      <c r="H12">
-        <v>18</v>
-      </c>
-      <c r="I12">
-        <v>15</v>
-      </c>
-      <c r="J12">
-        <v>85</v>
-      </c>
-      <c r="L12">
-        <v>81</v>
-      </c>
-      <c r="M12">
-        <v>19</v>
-      </c>
-      <c r="N12">
-        <v>42</v>
-      </c>
-      <c r="O12">
-        <v>58</v>
-      </c>
-      <c r="Q12">
-        <f t="shared" si="0"/>
-        <v>21.5</v>
-      </c>
-      <c r="R12">
-        <f t="shared" si="1"/>
-        <v>16.5</v>
-      </c>
-      <c r="S12">
-        <f t="shared" si="2"/>
-        <v>30.5</v>
-      </c>
-      <c r="T12">
-        <f t="shared" si="3"/>
-        <v>22.833333333333332</v>
-      </c>
-      <c r="U12">
-        <f t="shared" si="4"/>
-        <v>16.5</v>
-      </c>
-      <c r="V12">
-        <f t="shared" si="5"/>
-        <v>6.3333333333333321</v>
-      </c>
-    </row>
-    <row r="13" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B13">
-        <v>75</v>
-      </c>
-      <c r="C13">
-        <v>25</v>
-      </c>
-      <c r="D13">
-        <v>17</v>
-      </c>
-      <c r="E13">
-        <v>83</v>
-      </c>
-      <c r="G13">
-        <v>91</v>
-      </c>
-      <c r="H13">
-        <v>9</v>
-      </c>
-      <c r="I13">
-        <v>12</v>
-      </c>
-      <c r="J13">
-        <v>88</v>
-      </c>
-      <c r="L13">
-        <v>84</v>
-      </c>
-      <c r="M13">
-        <v>16</v>
-      </c>
-      <c r="N13">
-        <v>45</v>
-      </c>
-      <c r="O13">
-        <v>55</v>
-      </c>
-      <c r="Q13">
-        <f t="shared" si="0"/>
-        <v>21</v>
-      </c>
-      <c r="R13">
-        <f t="shared" si="1"/>
-        <v>10.5</v>
-      </c>
-      <c r="S13">
-        <f t="shared" si="2"/>
-        <v>30.5</v>
-      </c>
-      <c r="T13">
-        <f t="shared" si="3"/>
-        <v>20.666666666666668</v>
-      </c>
-      <c r="U13">
-        <f t="shared" si="4"/>
-        <v>10.5</v>
-      </c>
-      <c r="V13">
-        <f t="shared" si="5"/>
-        <v>10.166666666666668</v>
-      </c>
-    </row>
-    <row r="14" spans="1:32" x14ac:dyDescent="0.3">
-      <c r="B14">
-        <v>64</v>
-      </c>
-      <c r="C14">
-        <v>36</v>
-      </c>
-      <c r="D14">
-        <v>19</v>
-      </c>
-      <c r="E14">
-        <v>81</v>
-      </c>
-      <c r="G14">
-        <v>88</v>
-      </c>
-      <c r="H14">
-        <v>12</v>
-      </c>
-      <c r="I14">
-        <v>16</v>
-      </c>
-      <c r="J14">
-        <v>84</v>
-      </c>
-      <c r="L14">
-        <v>58</v>
-      </c>
-      <c r="M14">
-        <v>42</v>
-      </c>
-      <c r="N14">
-        <v>25</v>
-      </c>
-      <c r="O14">
-        <v>75</v>
-      </c>
-      <c r="Q14">
-        <f t="shared" si="0"/>
-        <v>27.5</v>
-      </c>
-      <c r="R14">
-        <f t="shared" si="1"/>
-        <v>14</v>
-      </c>
-      <c r="S14">
-        <f t="shared" si="2"/>
-        <v>33.5</v>
-      </c>
-      <c r="T14">
-        <f t="shared" si="3"/>
-        <v>25</v>
-      </c>
-      <c r="U14">
-        <f t="shared" si="4"/>
-        <v>14</v>
-      </c>
-      <c r="V14">
-        <f t="shared" si="5"/>
-        <v>11</v>
+        <v>7.6666666666666679</v>
       </c>
     </row>
     <row r="31" spans="17:26" x14ac:dyDescent="0.3">
@@ -2676,60 +1970,60 @@
         <v>0</v>
       </c>
       <c r="Q1" t="s">
-        <v>10</v>
+        <v>9</v>
       </c>
     </row>
     <row r="2" spans="1:32" x14ac:dyDescent="0.3">
       <c r="A2" t="s">
-        <v>17</v>
+        <v>16</v>
       </c>
       <c r="Q2" t="s">
+        <v>19</v>
+      </c>
+      <c r="R2" t="s">
         <v>20</v>
       </c>
-      <c r="R2" t="s">
+      <c r="S2" t="s">
         <v>21</v>
       </c>
-      <c r="S2" t="s">
-        <v>22</v>
-      </c>
       <c r="T2" t="s">
-        <v>12</v>
+        <v>11</v>
       </c>
       <c r="U2" t="s">
-        <v>14</v>
+        <v>13</v>
       </c>
       <c r="V2" t="s">
-        <v>11</v>
+        <v>10</v>
       </c>
       <c r="W2" t="s">
-        <v>30</v>
+        <v>28</v>
       </c>
       <c r="X2" t="s">
+        <v>23</v>
+      </c>
+      <c r="Y2" t="s">
+        <v>5</v>
+      </c>
+      <c r="Z2" t="s">
+        <v>24</v>
+      </c>
+      <c r="AA2" t="s">
+        <v>7</v>
+      </c>
+      <c r="AB2" t="s">
         <v>25</v>
-      </c>
-      <c r="Y2" t="s">
-        <v>6</v>
-      </c>
-      <c r="Z2" t="s">
-        <v>26</v>
-      </c>
-      <c r="AA2" t="s">
-        <v>8</v>
-      </c>
-      <c r="AB2" t="s">
-        <v>27</v>
       </c>
       <c r="AC2" t="s">
         <v>1</v>
       </c>
       <c r="AD2" t="s">
-        <v>13</v>
+        <v>12</v>
       </c>
       <c r="AE2" t="s">
+        <v>14</v>
+      </c>
+      <c r="AF2" t="s">
         <v>15</v>
-      </c>
-      <c r="AF2" t="s">
-        <v>16</v>
       </c>
     </row>
     <row r="3" spans="1:32" x14ac:dyDescent="0.3">
